--- a/docs/tables/voxel_iou_summary.xlsx
+++ b/docs/tables/voxel_iou_summary.xlsx
@@ -1854,7 +1854,6 @@
       <c r="J3" t="n">
         <v>4279</v>
       </c>
-      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2022,7 +2021,6 @@
       <c r="J7" t="n">
         <v>4024</v>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2190,7 +2188,6 @@
       <c r="J11" t="n">
         <v>8278</v>
       </c>
-      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2358,7 +2355,6 @@
       <c r="J15" t="n">
         <v>13029</v>
       </c>
-      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2526,7 +2522,6 @@
       <c r="J19" t="n">
         <v>886</v>
       </c>
-      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2694,7 +2689,6 @@
       <c r="J23" t="n">
         <v>799</v>
       </c>
-      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2862,7 +2856,6 @@
       <c r="J27" t="n">
         <v>1141</v>
       </c>
-      <c r="K27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3030,7 +3023,6 @@
       <c r="J31" t="n">
         <v>1142</v>
       </c>
-      <c r="K31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3198,7 +3190,6 @@
       <c r="J35" t="n">
         <v>2625</v>
       </c>
-      <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3366,7 +3357,6 @@
       <c r="J39" t="n">
         <v>1831</v>
       </c>
-      <c r="K39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3534,7 +3524,6 @@
       <c r="J43" t="n">
         <v>3051</v>
       </c>
-      <c r="K43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3702,7 +3691,6 @@
       <c r="J47" t="n">
         <v>3602</v>
       </c>
-      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3870,7 +3858,6 @@
       <c r="J51" t="n">
         <v>411</v>
       </c>
-      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4038,7 +4025,6 @@
       <c r="J55" t="n">
         <v>475</v>
       </c>
-      <c r="K55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4206,7 +4192,6 @@
       <c r="J59" t="n">
         <v>605</v>
       </c>
-      <c r="K59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4374,7 +4359,6 @@
       <c r="J63" t="n">
         <v>697</v>
       </c>
-      <c r="K63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4542,7 +4526,6 @@
       <c r="J67" t="n">
         <v>1662</v>
       </c>
-      <c r="K67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4710,7 +4693,6 @@
       <c r="J71" t="n">
         <v>1386</v>
       </c>
-      <c r="K71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4878,7 +4860,6 @@
       <c r="J75" t="n">
         <v>1826</v>
       </c>
-      <c r="K75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5046,7 +5027,6 @@
       <c r="J79" t="n">
         <v>2353</v>
       </c>
-      <c r="K79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5214,7 +5194,6 @@
       <c r="J83" t="n">
         <v>1448</v>
       </c>
-      <c r="K83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5382,7 +5361,6 @@
       <c r="J87" t="n">
         <v>1046</v>
       </c>
-      <c r="K87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5550,7 +5528,6 @@
       <c r="J91" t="n">
         <v>2013</v>
       </c>
-      <c r="K91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5718,7 +5695,6 @@
       <c r="J95" t="n">
         <v>3164</v>
       </c>
-      <c r="K95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7774,6 +7750,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
@@ -7785,22 +7762,11 @@
           <t>n = 24</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>0.951</v>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="10"/>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -7809,7 +7775,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Does not belong in chapter 5: IoU matches the F1@3cm ordering exactly on 2 of 6 objects, and every reordering it produces on the other 4 fails on inspection - see below. No new conclusion. Mention it in the methodology as an alternative that was considered, and leave it out of the results. The voxel sweep does reorder methods beyond the grid noise on bench_004, but singles out the same method ΔF1@10-3 already singles out there, so it restates the existing table rather than adding to it. Reorderings that were found but are smaller than the grid-origin noise, and so decide nothing: bench_004, bollard_003, bus_stop_002, information_sign_002. Caveat to state either way: the method ordering does not survive the grid-origin shift on bus_stop_002, information_sign_002, bench_004, bollard_003, so IoU cannot separate those methods at this voxel size.</t>
+          <t>IoU adds no ordering of its own: it matches the F1@3cm ordering exactly on 2 of 6 objects, and every reordering it produces on the other 4 fails on inspection - see below. So IoU confirms the F1 ordering rather than competing with it: a density-free check on the primary measure, not a second source of conclusions. The voxel sweep does reorder methods beyond the grid noise on bench_004, but singles out the same method ΔF1@10-3 already singles out there, so it restates the existing table rather than adding to it. Reorderings that were found but are smaller than the grid-origin noise, and so decide nothing: bench_004, bollard_003, bus_stop_002, information_sign_002. Caveat to state either way: the method ordering does not survive the grid-origin shift on bus_stop_002, information_sign_002, bench_004, bollard_003, so IoU cannot separate those methods at this voxel size.</t>
         </is>
       </c>
     </row>
